--- a/domain_model_setup.xlsx
+++ b/domain_model_setup.xlsx
@@ -2527,7 +2527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.179688000000001" defaultRowHeight="14.5"/>
   <cols>
     <col width="21.424911" customWidth="1" style="87" min="1" max="1"/>
@@ -3552,6 +3552,32 @@
       <c r="F40" s="115" t="inlineStr">
         <is>
           <t>How year-zero roughness was set: 0 surveyed and reproduced exactly, 1 surveyed but the deviate was clamped. Missing roughness is imputed before the run and cannot be detected here, so 2 (inferred) does not occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="115" t="inlineStr">
+        <is>
+          <t>par_rut_growth_yrs</t>
+        </is>
+      </c>
+      <c r="B41" s="115" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="69" t="n">
+        <v>999</v>
+      </c>
+      <c r="E41" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="115" t="inlineStr">
+        <is>
+          <t>Years of chipseal rut growth accumulated so far. Starts at 0 at year zero - NOT at the surface age, which would count the growth twice because the chipseal level model has no age term and already reproduces today's rut. Increments by 1 each period, is left alone by a resurfacing (a seal inherits the rut beneath it) and returns to 0 on a rehabilitation. Chipseal only; nothing reads it for asphalt.</t>
         </is>
       </c>
     </row>

--- a/domain_model_setup.xlsx
+++ b/domain_model_setup.xlsx
@@ -2527,7 +2527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.179688000000001" defaultRowHeight="14.5"/>
   <cols>
     <col width="21.424911" customWidth="1" style="87" min="1" max="1"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="C24" s="69" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="D24" s="69" t="n">
         <v>2.5</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="F24" s="115" t="inlineStr">
         <is>
-          <t>Estimated Rut increment, in mm/year</t>
+          <t>Realised change in rut depth over the period, in mm. DIAGNOSTIC ONLY - nothing reads it back to build the next value. The minimum is below zero because a treatment reset makes it negative, and the framework clamps every write silently: at a minimum of 0 the post-treatment drop this parameter exists to show would be recorded as 0 with nothing saying so.</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C26" s="69" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="D26" s="69" t="n">
         <v>5</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F26" s="115" t="inlineStr">
         <is>
-          <t>Estimated IRI Increment, in mm/m/year</t>
+          <t>Realised change in IRI over the period, in mm/m. DIAGNOSTIC ONLY. The minimum is below zero for the same reason as par_rut_increm: a treatment reset makes it negative and a clamped write is silent.</t>
         </is>
       </c>
     </row>
@@ -3578,6 +3578,32 @@
       <c r="F41" s="115" t="inlineStr">
         <is>
           <t>Years of chipseal rut growth accumulated so far. Starts at 0 at year zero - NOT at the surface age, which would count the growth twice because the chipseal level model has no age term and already reproduces today's rut. Increments by 1 each period, is left alone by a resurfacing (a seal inherits the rut beneath it) and returns to 0 on a rehabilitation. Chipseal only; nothing reads it for asphalt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="115" t="inlineStr">
+        <is>
+          <t>par_rehab_flag</t>
+        </is>
+      </c>
+      <c r="B42" s="115" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="115" t="inlineStr">
+        <is>
+          <t>1 once the model has rehabilitated this segment, 0 otherwise. Carries the permanent as-new offsets of the 'rehab_offsets' lookup set into every later period: the fitted models were built entirely on surfacings over old pavements (median pavement age 63 years), so their age-zero prediction means 'a fresh surface on an old pavement' and would snap a rebuilt segment straight back to 3.66 mm of rut or IRI 5.72. Never returns to 0 - a later reseal does not undo the fact that the pavement underneath is new.</t>
         </is>
       </c>
     </row>
